--- a/cet4/result/42_悬疑女王_农场的神秘往事/42_悬疑女王_农场的神秘往事_学习版.xlsx
+++ b/cet4/result/42_悬疑女王_农场的神秘往事/42_悬疑女王_农场的神秘往事_学习版.xlsx
@@ -397,941 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>northern</v>
       </c>
       <c r="B2" t="str">
-        <v>northern</v>
+        <v>/ˈnɔːrðərn/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>北方的</v>
       </c>
-      <c r="D2" t="str">
-        <v>northern(北方的)</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>Wednesday</v>
       </c>
       <c r="B3" t="str">
-        <v>Wednesday</v>
+        <v>/'wenzdei/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>星期三</v>
       </c>
-      <c r="D3" t="str">
-        <v>Wednesday(星期三)</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>missing</v>
       </c>
       <c r="B4" t="str">
-        <v>missing</v>
+        <v>/ˈmɪsɪŋ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>失踪的</v>
       </c>
-      <c r="D4" t="str">
-        <v>missing(失踪的)</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>traffic</v>
       </c>
       <c r="B5" t="str">
-        <v>traffic</v>
+        <v>/ˈtræfɪk/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>交通</v>
       </c>
-      <c r="D5" t="str">
-        <v>traffic(交通)</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>space</v>
       </c>
       <c r="B6" t="str">
-        <v>space</v>
+        <v>/speɪs/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>空间</v>
       </c>
-      <c r="D6" t="str">
-        <v>space(空间)</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>fence</v>
       </c>
       <c r="B7" t="str">
-        <v>fence</v>
+        <v>/fens/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>栅栏</v>
       </c>
-      <c r="D7" t="str">
-        <v>fence(栅栏)</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>tough</v>
       </c>
       <c r="B8" t="str">
-        <v>tough</v>
+        <v>/tʌf/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./v./adj./adv.</v>
+      </c>
+      <c r="D8" t="str">
         <v>强硬的</v>
       </c>
-      <c r="D8" t="str">
-        <v>tough(强硬的)</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>ask</v>
       </c>
       <c r="B9" t="str">
-        <v>ask</v>
+        <v>/æsk/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>询问</v>
       </c>
-      <c r="D9" t="str">
-        <v>ask(询问)</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>buckle</v>
       </c>
       <c r="B10" t="str">
-        <v>buckle</v>
+        <v>/ˈbʌkl/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D10" t="str">
         <v>皮带扣</v>
       </c>
-      <c r="D10" t="str">
-        <v>buckle(皮带扣)</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>wise</v>
       </c>
       <c r="B11" t="str">
-        <v>wise</v>
+        <v>/waɪz/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>明智的</v>
       </c>
-      <c r="D11" t="str">
-        <v>wise(明智的)</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>maid</v>
       </c>
       <c r="B12" t="str">
-        <v>maid</v>
+        <v>/meɪd/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>女仆</v>
       </c>
-      <c r="D12" t="str">
-        <v>maid(女仆)</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>tour</v>
       </c>
       <c r="B13" t="str">
-        <v>tour</v>
+        <v>/tʊr/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>游览</v>
       </c>
-      <c r="D13" t="str">
-        <v>tour(游览)</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>enthusiastic</v>
       </c>
       <c r="B14" t="str">
-        <v>enthusiastic</v>
+        <v>/ɪnˌθuːziˈæstɪk/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>热情的</v>
       </c>
-      <c r="D14" t="str">
-        <v>enthusiastic(热情的)</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>groan</v>
       </c>
       <c r="B15" t="str">
-        <v>groan</v>
+        <v>/ɡroʊn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>呻吟</v>
       </c>
-      <c r="D15" t="str">
-        <v>groan(呻吟)</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>shed</v>
       </c>
       <c r="B16" t="str">
-        <v>shed</v>
+        <v>/ʃed/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>棚屋</v>
       </c>
-      <c r="D16" t="str">
-        <v>shed(棚屋)</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>instrument</v>
       </c>
       <c r="B17" t="str">
-        <v>instrument</v>
+        <v>/ˈɪnstrəmənt/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D17" t="str">
         <v>工具</v>
       </c>
-      <c r="D17" t="str">
-        <v>instrument(工具)</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>pump</v>
       </c>
       <c r="B18" t="str">
-        <v>pump</v>
+        <v>/pʌmp/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>泵</v>
       </c>
-      <c r="D18" t="str">
-        <v>pump(泵)</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>inexpensive</v>
       </c>
       <c r="B19" t="str">
-        <v>inexpensive</v>
+        <v>/ˌɪnɪkˈspensɪv/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>廉价的</v>
       </c>
-      <c r="D19" t="str">
-        <v>inexpensive(廉价的)</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>fertilizer</v>
       </c>
       <c r="B20" t="str">
-        <v>fertilizer</v>
+        <v>/ˈfɜːrtəlaɪzər/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>化肥</v>
       </c>
-      <c r="D20" t="str">
-        <v>fertilizer(化肥)</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>fridge</v>
       </c>
       <c r="B21" t="str">
-        <v>fridge</v>
+        <v>/frɪdʒ/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>冰箱</v>
       </c>
-      <c r="D21" t="str">
-        <v>fridge(冰箱)</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>door</v>
       </c>
       <c r="B22" t="str">
-        <v>door</v>
+        <v>/dɔːr/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>门</v>
       </c>
-      <c r="D22" t="str">
-        <v>door(门)</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>poison</v>
       </c>
       <c r="B23" t="str">
-        <v>poison</v>
+        <v>/ˈpɔɪzn/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>毒药</v>
       </c>
-      <c r="D23" t="str">
-        <v>poison(毒药)</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>curtain</v>
       </c>
       <c r="B24" t="str">
-        <v>curtain</v>
+        <v>/ˈkɜːrtn/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D24" t="str">
         <v>窗帘</v>
       </c>
-      <c r="D24" t="str">
-        <v>curtain(窗帘)</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>cushion</v>
       </c>
       <c r="B25" t="str">
-        <v>cushion</v>
+        <v>/ˈkʊʃn/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D25" t="str">
         <v>靠垫</v>
       </c>
-      <c r="D25" t="str">
-        <v>cushion(靠垫)</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>consult</v>
       </c>
       <c r="B26" t="str">
-        <v>consult</v>
+        <v>/kənˈsʌlt/</v>
       </c>
       <c r="C26" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D26" t="str">
         <v>咨询</v>
       </c>
-      <c r="D26" t="str">
-        <v>consult(咨询)</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>bat</v>
       </c>
       <c r="B27" t="str">
-        <v>shed</v>
+        <v>/bæt/</v>
       </c>
       <c r="C27" t="str">
-        <v>棚屋</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>shed(棚屋)</v>
+        <v>蝙蝠</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>forward</v>
       </c>
       <c r="B28" t="str">
-        <v>bat</v>
+        <v>/ˈfɔːrwərd/</v>
       </c>
       <c r="C28" t="str">
-        <v>蝙蝠</v>
+        <v>n./vt./v./adj./adv.</v>
       </c>
       <c r="D28" t="str">
-        <v>bat(蝙蝠)</v>
+        <v>向前</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>bury</v>
       </c>
       <c r="B29" t="str">
-        <v>forward</v>
+        <v>/ˈberi/</v>
       </c>
       <c r="C29" t="str">
-        <v>向前</v>
+        <v>n./vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>forward(向前)</v>
+        <v>埋葬</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>status</v>
       </c>
       <c r="B30" t="str">
-        <v>bury</v>
+        <v>/ˈsteɪtəs/</v>
       </c>
       <c r="C30" t="str">
-        <v>埋葬</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>bury(埋葬)</v>
+        <v>地位</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>rouse</v>
       </c>
       <c r="B31" t="str">
-        <v>status</v>
+        <v>/raʊz/</v>
       </c>
       <c r="C31" t="str">
-        <v>地位</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>status(地位)</v>
+        <v>唤醒</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>into</v>
       </c>
       <c r="B32" t="str">
-        <v>rouse</v>
+        <v>/ˈɪntuː/</v>
       </c>
       <c r="C32" t="str">
-        <v>唤醒</v>
+        <v>n./prep.</v>
       </c>
       <c r="D32" t="str">
-        <v>rouse(唤醒)</v>
+        <v>进入</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>basis</v>
       </c>
       <c r="B33" t="str">
-        <v>into</v>
+        <v>/ˈbeɪsɪs/</v>
       </c>
       <c r="C33" t="str">
-        <v>进入</v>
+        <v>n.</v>
       </c>
       <c r="D33" t="str">
-        <v>into(进入)</v>
+        <v>基础</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>image</v>
       </c>
       <c r="B34" t="str">
-        <v>basis</v>
+        <v>/ˈɪmɪdʒ/</v>
       </c>
       <c r="C34" t="str">
-        <v>基础</v>
+        <v>n./vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>basis(基础)</v>
+        <v>图像</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>raid</v>
       </c>
       <c r="B35" t="str">
-        <v>image</v>
+        <v>/reɪd/</v>
       </c>
       <c r="C35" t="str">
-        <v>图像</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>image(图像)</v>
+        <v>突袭</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>emit</v>
       </c>
       <c r="B36" t="str">
-        <v>raid</v>
+        <v>/iˈmɪt/</v>
       </c>
       <c r="C36" t="str">
-        <v>突袭</v>
+        <v>vt.</v>
       </c>
       <c r="D36" t="str">
-        <v>raid(突袭)</v>
+        <v>排放</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>mankind</v>
       </c>
       <c r="B37" t="str">
-        <v>emit</v>
+        <v>/mænˈkaɪnd/</v>
       </c>
       <c r="C37" t="str">
-        <v>排放</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>emit(排放)</v>
+        <v>人类</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>pint</v>
       </c>
       <c r="B38" t="str">
-        <v>mankind</v>
+        <v>/paɪnt/</v>
       </c>
       <c r="C38" t="str">
-        <v>人类</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>mankind(人类)</v>
+        <v>品脱</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>grammar</v>
       </c>
       <c r="B39" t="str">
-        <v>Wednesday</v>
+        <v>/ˈɡræmər/</v>
       </c>
       <c r="C39" t="str">
-        <v>星期三</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>Wednesday(星期三)</v>
+        <v>语法</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>chance</v>
       </c>
       <c r="B40" t="str">
-        <v>pint</v>
+        <v>/tʃæns/</v>
       </c>
       <c r="C40" t="str">
-        <v>品脱</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>pint(品脱)</v>
+        <v>机会</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>convenience</v>
       </c>
       <c r="B41" t="str">
-        <v>grammar</v>
+        <v>/kənˈviːniəns/</v>
       </c>
       <c r="C41" t="str">
-        <v>语法</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>grammar(语法)</v>
+        <v>便利</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>digest</v>
       </c>
       <c r="B42" t="str">
-        <v>chance</v>
+        <v>/daɪˈdʒest/</v>
       </c>
       <c r="C42" t="str">
-        <v>机会</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>chance(机会)</v>
+        <v>消化</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>naked</v>
       </c>
       <c r="B43" t="str">
-        <v>wise</v>
+        <v>/ˈneɪkɪd/</v>
       </c>
       <c r="C43" t="str">
-        <v>明智的</v>
+        <v>adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>wise(明智的)</v>
+        <v>裸露的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>cost</v>
       </c>
       <c r="B44" t="str">
-        <v>convenience</v>
+        <v>/kɔːst/</v>
       </c>
       <c r="C44" t="str">
-        <v>便利</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>convenience(便利)</v>
+        <v>成本</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>trip</v>
       </c>
       <c r="B45" t="str">
-        <v>digest</v>
+        <v>/trɪp/</v>
       </c>
       <c r="C45" t="str">
-        <v>消化</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>digest(消化)</v>
+        <v>旅程</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>now</v>
       </c>
       <c r="B46" t="str">
-        <v>fertilizer</v>
+        <v>/naʊ/</v>
       </c>
       <c r="C46" t="str">
-        <v>化肥</v>
+        <v>n./v./adj./adv./conj.</v>
       </c>
       <c r="D46" t="str">
-        <v>fertilizer(化肥)</v>
+        <v>现在</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>spectacle</v>
       </c>
       <c r="B47" t="str">
-        <v>naked</v>
+        <v>/ˈspektəkl/</v>
       </c>
       <c r="C47" t="str">
-        <v>裸露的</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>naked(裸露的)</v>
+        <v>景象</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>saddle</v>
       </c>
       <c r="B48" t="str">
-        <v>cost</v>
+        <v>/ˈsædl/</v>
       </c>
       <c r="C48" t="str">
-        <v>成本</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>cost(成本)</v>
+        <v>马鞍</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>melt</v>
       </c>
       <c r="B49" t="str">
-        <v>trip</v>
+        <v>/melt/</v>
       </c>
       <c r="C49" t="str">
-        <v>旅程</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>trip(旅程)</v>
+        <v>融化</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>approximate</v>
       </c>
       <c r="B50" t="str">
-        <v>now</v>
+        <v>/əˈprɑːksɪmət/</v>
       </c>
       <c r="C50" t="str">
-        <v>现在</v>
+        <v>v./adj.</v>
       </c>
       <c r="D50" t="str">
-        <v>now(现在)</v>
+        <v>近似的</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>why</v>
       </c>
       <c r="B51" t="str">
-        <v>spectacle</v>
+        <v>/waɪ/</v>
       </c>
       <c r="C51" t="str">
-        <v>景象</v>
+        <v>n./v./adv./int.</v>
       </c>
       <c r="D51" t="str">
-        <v>spectacle(景象)</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>inexpensive</v>
-      </c>
-      <c r="C52" t="str">
-        <v>廉价的</v>
-      </c>
-      <c r="D52" t="str">
-        <v>inexpensive(廉价的)</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>saddle</v>
-      </c>
-      <c r="C53" t="str">
-        <v>马鞍</v>
-      </c>
-      <c r="D53" t="str">
-        <v>saddle(马鞍)</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>melt</v>
-      </c>
-      <c r="C54" t="str">
-        <v>融化</v>
-      </c>
-      <c r="D54" t="str">
-        <v>melt(融化)</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>approximate</v>
-      </c>
-      <c r="C55" t="str">
-        <v>近似的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>approximate(近似的)</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>image</v>
-      </c>
-      <c r="C56" t="str">
-        <v>图像</v>
-      </c>
-      <c r="D56" t="str">
-        <v>image(图像)</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>space</v>
-      </c>
-      <c r="C57" t="str">
-        <v>空间</v>
-      </c>
-      <c r="D57" t="str">
-        <v>space(空间)</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>status</v>
-      </c>
-      <c r="C58" t="str">
-        <v>地位</v>
-      </c>
-      <c r="D58" t="str">
-        <v>status(地位)</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>raid</v>
-      </c>
-      <c r="C59" t="str">
-        <v>突袭</v>
-      </c>
-      <c r="D59" t="str">
-        <v>raid(突袭)</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>naked</v>
-      </c>
-      <c r="C60" t="str">
-        <v>无遮掩的</v>
-      </c>
-      <c r="D60" t="str">
-        <v>naked(无遮掩的)</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>enthusiastic</v>
-      </c>
-      <c r="C61" t="str">
-        <v>热情的</v>
-      </c>
-      <c r="D61" t="str">
-        <v>enthusiastic(热情的)</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>tough</v>
-      </c>
-      <c r="C62" t="str">
-        <v>艰难的</v>
-      </c>
-      <c r="D62" t="str">
-        <v>tough(艰难的)</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>why</v>
-      </c>
-      <c r="C63" t="str">
         <v>为什么</v>
-      </c>
-      <c r="D63" t="str">
-        <v>why(为什么)</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>missing</v>
-      </c>
-      <c r="C64" t="str">
-        <v>失踪的</v>
-      </c>
-      <c r="D64" t="str">
-        <v>missing(失踪的)</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>northern</v>
-      </c>
-      <c r="C65" t="str">
-        <v>北方的</v>
-      </c>
-      <c r="D65" t="str">
-        <v>northern(北方的)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>wise</v>
-      </c>
-      <c r="C66" t="str">
-        <v>明智的</v>
-      </c>
-      <c r="D66" t="str">
-        <v>wise(明智的)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>